--- a/Assets/Resources/sceneData.xlsx
+++ b/Assets/Resources/sceneData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10125" windowHeight="7717"/>
+    <workbookView windowWidth="21600" windowHeight="10695"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
-  <si>
-    <t>未知</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+  <si>
+    <t>医院</t>
   </si>
   <si>
     <t>yiyuan</t>
@@ -49,9 +49,6 @@
     <t>xuexiao</t>
   </si>
   <si>
-    <t>医院</t>
-  </si>
-  <si>
     <t>救济站</t>
   </si>
   <si>
@@ -113,6 +110,12 @@
   </si>
   <si>
     <t>shourongsuo</t>
+  </si>
+  <si>
+    <t>洛杉矶</t>
+  </si>
+  <si>
+    <t>luoshanji</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1081,7 +1084,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -1092,10 +1095,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1103,10 +1106,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1114,10 +1117,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1125,10 +1128,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -1136,10 +1139,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -1147,10 +1150,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1158,10 +1161,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>11</v>
@@ -1169,10 +1172,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
         <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
       </c>
       <c r="C12">
         <v>12</v>
@@ -1180,10 +1183,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
       </c>
       <c r="C13">
         <v>13</v>
@@ -1191,10 +1194,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
         <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
       </c>
       <c r="C14">
         <v>14</v>
@@ -1202,10 +1205,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
         <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
       </c>
       <c r="C15">
         <v>15</v>
@@ -1213,13 +1216,24 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
         <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
       </c>
       <c r="C16">
         <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
